--- a/Degree.xlsx
+++ b/Degree.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Documents\Projet IA\Dashboard_CV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D4523E-13DB-4813-8126-CEBC23A0A91E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFBC0083-D44C-460D-B4ED-8D7004A75764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -440,10 +440,10 @@
         <v>9</v>
       </c>
       <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
         <v>22</v>
-      </c>
-      <c r="F1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
